--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBVersions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBCustomizations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -182,6 +184,11 @@
         <t>Full name is computed from the first and last name of the customer</t>
       </text>
     </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Identifier for the customers.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -475,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -484,6 +491,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,40 +503,49 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>EmailAddress</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FirstName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LastName</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FullName</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>EmailAddress</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>FirstName</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LastName</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FullName</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>From_field_Customer</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CUST0001</t>
-        </is>
+          <t>jane-smith-email-com</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE($C2, "@", "-")</f>
+        <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -536,7 +554,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -548,17 +566,18 @@
         <f>$E2 &amp; ", " &amp; $D2</f>
         <v/>
       </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CUST0002</t>
-        </is>
+          <t>john-doe-email-com</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE($C3, "@", "-")</f>
+        <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -567,7 +586,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -579,17 +598,18 @@
         <f>$E3 &amp; ", " &amp; $D3</f>
         <v/>
       </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CUST0003</t>
-        </is>
+          <t>emily-jones-email-com</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE($C4, "@", "-")</f>
+        <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -598,7 +618,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -610,9 +630,356 @@
         <f>$E4 &amp; ", " &amp; $D4</f>
         <v/>
       </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ERBVersionId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>BaseId</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CommitDate</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IsPublished</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ERBCustomizationId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SQLCode</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SQLTarget</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CustomizationType</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>03a-customize-schema-sql</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>03a-customize-schema.sql</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Customize Schema</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE SCHEMA - User-defined tables and schema modifications
+-- ============================================================================
+-- This file is for YOUR custom schema changes that should persist across
+-- regeneration of the base ERB files.
+--
+-- USE THIS FILE FOR:
+--   - Additional tables not defined in the rulebook
+--   - Extra columns on existing tables (ALTER TABLE)
+--   - Custom indexes for performance tuning
+--   - Custom constraints or triggers
+--
+-- IMPORTANT:
+--   - This file runs AFTER 01-drop-and-create-tables.sql
+--   - The base tables already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom schema changes go here:
+</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>03b-customize-functions-sql</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>03b-customize-functions.sql</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Customize Functions</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE FUNCTIONS - User-defined calculation functions
+-- ============================================================================
+-- This file is for YOUR custom PostgreSQL functions that should persist
+-- across regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 02-create-functions.sql
+--   - Base ERB calc functions already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom functions go here:
+</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>03c-customize-views-sql</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>03c-customize-views.sql</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Customize Views</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE VIEWS - User-defined views and view extensions
+-- ============================================================================
+-- This file is for YOUR custom views that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 03-create-views.sql
+--   - All base vw_* views already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom views go here:
+</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Views</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>03d-customize-rls-sql</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>03d-customize-rls.sql</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Customize Policies (RLS)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE POLICIES - User-defined Row Level Security policies
+-- ============================================================================
+-- This file is for YOUR custom RLS policies that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 04-create-policies.sql
+--   - Base RLS policies already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom policies go here:
+</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>RLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data-sql</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data.sql</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Customize Data (Seeds / Migrations)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE DATA - User-defined seed data and data migrations
+-- ============================================================================
+-- This file is for YOUR custom seed data that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 05-insert-data.sql
+--   - Base seed data already exists when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom data inserts go here:
+</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBVersions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBCustomizations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -184,11 +182,6 @@
         <t>Full name is computed from the first and last name of the customer</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Identifier for the customers.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -482,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -491,8 +484,6 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,16 +517,6 @@
           <t>FullName</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>From_field_Customer</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -566,8 +547,6 @@
         <f>$E2 &amp; ", " &amp; $D2</f>
         <v/>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,8 +577,6 @@
         <f>$E3 &amp; ", " &amp; $D3</f>
         <v/>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -630,356 +607,9 @@
         <f>$E4 &amp; ", " &amp; $D4</f>
         <v/>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ERBVersionId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>BaseId</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CommitDate</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>IsPublished</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ERBCustomizationId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SQLCode</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SQLTarget</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CustomizationType</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>03a-customize-schema-sql</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>03a-customize-schema.sql</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Customize Schema</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE SCHEMA - User-defined tables and schema modifications
--- ============================================================================
--- This file is for YOUR custom schema changes that should persist across
--- regeneration of the base ERB files.
---
--- USE THIS FILE FOR:
---   - Additional tables not defined in the rulebook
---   - Extra columns on existing tables (ALTER TABLE)
---   - Custom indexes for performance tuning
---   - Custom constraints or triggers
---
--- IMPORTANT:
---   - This file runs AFTER 01-drop-and-create-tables.sql
---   - The base tables already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom schema changes go here:
-</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>03b-customize-functions-sql</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>03b-customize-functions.sql</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Customize Functions</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE FUNCTIONS - User-defined calculation functions
--- ============================================================================
--- This file is for YOUR custom PostgreSQL functions that should persist
--- across regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 02-create-functions.sql
---   - Base ERB calc functions already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom functions go here:
-</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Functions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>03c-customize-views-sql</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>03c-customize-views.sql</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Customize Views</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE VIEWS - User-defined views and view extensions
--- ============================================================================
--- This file is for YOUR custom views that should persist across
--- regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 03-create-views.sql
---   - All base vw_* views already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom views go here:
-</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Views</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>03d-customize-rls-sql</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>03d-customize-rls.sql</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Customize Policies (RLS)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE POLICIES - User-defined Row Level Security policies
--- ============================================================================
--- This file is for YOUR custom RLS policies that should persist across
--- regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 04-create-policies.sql
---   - Base RLS policies already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom policies go here:
-</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>RLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>03e-customize-data-sql</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>03e-customize-data.sql</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Customize Data (Seeds / Migrations)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE DATA - User-defined seed data and data migrations
--- ============================================================================
--- This file is for YOUR custom seed data that should persist across
--- regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 05-insert-data.sql
---   - Base seed data already exists when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom data inserts go here:
-</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bobby</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F2" s="3">
-        <f>$E2 &amp; ", " &amp; $D2</f>
+        <f>$D2 &amp; " " &amp; $E2</f>
         <v/>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="F3" s="3">
-        <f>$E3 &amp; ", " &amp; $D3</f>
+        <f>$D3 &amp; " " &amp; $E3</f>
         <v/>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="F4" s="3">
-        <f>$E4 &amp; ", " &amp; $D4</f>
+        <f>$D4 &amp; " " &amp; $E4</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__meta__" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -159,7 +160,7 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Identifier for the customers.</t>
+        <t>Full name is computed from the first and last name of the customer</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -169,17 +170,52 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>First Name of the customer - used to make the full name</t>
+        <t>dsfdfds</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Last Name of the customer - used to make the full name</t>
+        <t>First Name of the customer - used to make the full name</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Full name is computed from the first and last name of the customer</t>
+        <t>Last Name of the customer - used to make the full name</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>The metadata key (e.g. 'tagline', 'motif_palette', 'substrates'). Unique within the table.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Identifier for this metadata entry. Mirrors MetaKey so the row is addressable by Name like every other table.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>How to interpret the value columns: 'string' (use StringValue), 'object' (parse JsonValue as JSON object), 'array' (parse JsonValue as JSON array).</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Plain string value. Populated when ValueType == 'string'; null otherwise.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>JSON-encoded value. Populated when ValueType == 'object' or 'array'; null when ValueType == 'string'.</t>
       </text>
     </comment>
   </commentList>
@@ -475,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -504,17 +540,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Initials</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LastName</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FullName</t>
         </is>
       </c>
     </row>
@@ -525,7 +561,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>SUBSTITUTE($C2, "@", "-")</f>
+        <f>$F2 &amp; ", " &amp; $E2</f>
         <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -533,19 +569,19 @@
           <t>jane.smith@email.com</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
+      <c r="D2" s="3">
+        <f>LEFT($E2, 1) &amp; LEFT($F2, 1) &amp; "."</f>
+        <v/>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="F2" s="3">
-        <f>$D2 &amp; " " &amp; $E2</f>
-        <v/>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Smithy</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -555,7 +591,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>SUBSTITUTE($C3, "@", "-")</f>
+        <f>$F3 &amp; ", " &amp; $E3</f>
         <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -563,19 +599,19 @@
           <t>john.doe@email.com</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Jimmy</t>
-        </is>
+      <c r="D3" s="3">
+        <f>LEFT($E3, 1) &amp; LEFT($F3, 1) &amp; "."</f>
+        <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Doe</t>
         </is>
-      </c>
-      <c r="F3" s="3">
-        <f>$D3 &amp; " " &amp; $E3</f>
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -585,7 +621,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>SUBSTITUTE($C4, "@", "-")</f>
+        <f>$F4 &amp; ", " &amp; $E4</f>
         <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -593,19 +629,275 @@
           <t>emily.jones@email.com</t>
         </is>
       </c>
+      <c r="D4" s="3">
+        <f>LEFT($E4, 1) &amp; LEFT($F4, 1) &amp; "."</f>
+        <v/>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>alice-cooper</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>$F5 &amp; ", " &amp; $E5</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>alice@cooper.com</t>
+        </is>
+      </c>
+      <c r="D5" s="3">
+        <f>LEFT($E5, 1) &amp; LEFT($F5, 1) &amp; "."</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Gutknecht</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MetaKey</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ValueType</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>StringValue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>JsonValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>tagline</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>$A2</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>One table. One calculated field. That's the whole demo.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>motif</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>$A3</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>description_rich</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>$A4</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mary</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="F4" s="3">
-        <f>$D4 &amp; " " &amp; $E4</f>
-        <v/>
+          <t>The smallest non-trivial Effortless rulebook. **One** entity (`Customers`), three rows, and a single calculated field — `FullName = FirstName &amp; " " &amp; LastName`. The argument is the simplicity itself: this much logic, lifted out of application code and into the rulebook, propagates to every substrate. Postgres view, Python class, Excel cell, OWL ontology — all four compute the same answer the same way, from the same rulebook JSON, with zero glue code.
+This is the rulebook to point a skeptic at when *every other demo feels like too much*.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>use_cases</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>$A5</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>["**Edit `FirstName` on any row and watch `FullName` recompute in every substrate.** No application code reads this field — the rulebook IS the field.", "**Compare the Postgres view, the Python class, and the Excel cell** for the same row. They all compute `FullName` from the same formula declared once in the rulebook.", "**Try adding a calculated field of your own** — say `Initials = LEFT(FirstName, 1) &amp; LEFT(LastName, 1)`. Run `effortless build`. Every substrate now has it."]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>signature_rows</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>$A6</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[{"entity": "Customers", "ids": ["jane-smith-email-com", "john-doe-email-com", "emily-jones-email-com"]}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>journal_seed</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>$A7</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Three customers. One calculated field. The whole point of ERB, on a napkin.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>substrates</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>$A8</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>[{"key": "postgres", "important": true, "chip_label": "Postgres"}, {"key": "python", "important": true, "chip_label": "Python"}, {"key": "excel", "important": false, "chip_label": "Excel"}, {"key": "owl", "important": false, "chip_label": "OWL"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>motif_palette</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>$A9</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>{"primary": "#2b4a6a", "accent": "#e6a544", "ink": "#0d1b2a"}</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__meta__" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -186,6 +187,41 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>The metadata key (e.g. 'tagline', 'motif_palette', 'substrates'). Unique within the table.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Identifier for this metadata entry. Mirrors MetaKey so the row is addressable by Name like every other table.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>How to interpret the value columns: 'string' (use StringValue), 'object' (parse JsonValue as JSON object), 'array' (parse JsonValue as JSON array).</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Plain string value. Populated when ValueType == 'string'; null otherwise.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>JSON-encoded value. Populated when ValueType == 'object' or 'array'; null when ValueType == 'string'.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -612,4 +648,230 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MetaKey</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ValueType</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>StringValue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>JsonValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>tagline</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>$A2</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>One table. One calculated field. That's the whole demo.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>motif</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>$A3</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>description_rich</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>$A4</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>The smallest non-trivial Effortless rulebook. **One** entity (`Customers`), three rows, and a single calculated field — `FullName = FirstName &amp; " " &amp; LastName`. The argument is the simplicity itself: this much logic, lifted out of application code and into the rulebook, propagates to every substrate. Postgres view, Python class, Excel cell, OWL ontology — all four compute the same answer the same way, from the same rulebook JSON, with zero glue code.
+This is the rulebook to point a skeptic at when *every other demo feels like too much*.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>use_cases</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>$A5</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>["**Edit `FirstName` on any row and watch `FullName` recompute in every substrate.** No application code reads this field — the rulebook IS the field.", "**Compare the Postgres view, the Python class, and the Excel cell** for the same row. They all compute `FullName` from the same formula declared once in the rulebook.", "**Try adding a calculated field of your own** — say `Initials = LEFT(FirstName, 1) &amp; LEFT(LastName, 1)`. Run `effortless build`. Every substrate now has it."]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>signature_rows</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>$A6</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[{"entity": "Customers", "ids": ["jane-smith-email-com", "john-doe-email-com", "emily-jones-email-com"]}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>journal_seed</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>$A7</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Three customers. One calculated field. The whole point of ERB, on a napkin.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>substrates</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>$A8</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>[{"key": "postgres", "important": true, "chip_label": "Postgres"}, {"key": "python", "important": true, "chip_label": "Python"}, {"key": "excel", "important": false, "chip_label": "Excel"}, {"key": "owl", "important": false, "chip_label": "OWL"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>motif_palette</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>$A9</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>{"primary": "#2b4a6a", "accent": "#e6a544", "ink": "#0d1b2a"}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>
--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -170,15 +170,20 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
+        <t>dsfdfds</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
         <t>First Name of the customer - used to make the full name</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>Last Name of the customer - used to make the full name</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>Full name is computed from the first and last name of the customer</t>
       </text>
@@ -511,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -520,6 +525,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,15 +546,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Initials</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>FullName</t>
         </is>
@@ -569,18 +580,23 @@
           <t>jane.smith@email.com</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>LEFT(FirstName, 1) &amp; LEFT(LastName, 1)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Jane</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Smith</t>
         </is>
       </c>
-      <c r="F2" s="3">
-        <f>$D2 &amp; " " &amp; $E2</f>
+      <c r="G2" s="3">
+        <f>$E2 &amp; " " &amp; $F2</f>
         <v/>
       </c>
     </row>
@@ -599,18 +615,23 @@
           <t>john.doe@email.com</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>LEFT(FirstName, 1) &amp; LEFT(LastName, 1)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Jimmy</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Doe</t>
         </is>
       </c>
-      <c r="F3" s="3">
-        <f>$D3 &amp; " " &amp; $E3</f>
+      <c r="G3" s="3">
+        <f>$E3 &amp; " " &amp; $F3</f>
         <v/>
       </c>
     </row>
@@ -629,18 +650,23 @@
           <t>emily.jones@email.com</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>LEFT(FirstName, 1) &amp; LEFT(LastName, 1)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Mary</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Jones</t>
         </is>
       </c>
-      <c r="F4" s="3">
-        <f>$D4 &amp; " " &amp; $E4</f>
+      <c r="G4" s="3">
+        <f>$E4 &amp; " " &amp; $F4</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -580,10 +580,9 @@
           <t>jane.smith@email.com</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>LEFT(FirstName, 1) &amp; LEFT(LastName, 1)</t>
-        </is>
+      <c r="D2" s="3">
+        <f>LEFT($F2, 1) &amp; LEFT($E2, 1)</f>
+        <v/>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -596,7 +595,7 @@
         </is>
       </c>
       <c r="G2" s="3">
-        <f>$E2 &amp; " " &amp; $F2</f>
+        <f>$F2 &amp; " -*- " &amp; $E2</f>
         <v/>
       </c>
     </row>
@@ -615,10 +614,9 @@
           <t>john.doe@email.com</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>LEFT(FirstName, 1) &amp; LEFT(LastName, 1)</t>
-        </is>
+      <c r="D3" s="3">
+        <f>LEFT($F3, 1) &amp; LEFT($E3, 1)</f>
+        <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -631,7 +629,7 @@
         </is>
       </c>
       <c r="G3" s="3">
-        <f>$E3 &amp; " " &amp; $F3</f>
+        <f>$F3 &amp; " -*- " &amp; $E3</f>
         <v/>
       </c>
     </row>
@@ -650,10 +648,9 @@
           <t>emily.jones@email.com</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>LEFT(FirstName, 1) &amp; LEFT(LastName, 1)</t>
-        </is>
+      <c r="D4" s="3">
+        <f>LEFT($F4, 1) &amp; LEFT($E4, 1)</f>
+        <v/>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -666,7 +663,7 @@
         </is>
       </c>
       <c r="G4" s="3">
-        <f>$E4 &amp; " " &amp; $F4</f>
+        <f>$F4 &amp; " -*- " &amp; $E4</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -581,12 +581,12 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>LEFT($F2, 1) &amp; LEFT($E2, 1)</f>
+        <f>$E2 &amp; " " &amp; LEFT($F2, 1) &amp; "."</f>
         <v/>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="G2" s="3">
-        <f>$F2 &amp; " -*- " &amp; $E2</f>
+        <f>$E2 &amp; " " &amp; $F2</f>
         <v/>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>LEFT($F3, 1) &amp; LEFT($E3, 1)</f>
+        <f>$E3 &amp; " " &amp; LEFT($F3, 1) &amp; "."</f>
         <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G3" s="3">
-        <f>$F3 &amp; " -*- " &amp; $E3</f>
+        <f>$E3 &amp; " " &amp; $F3</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D4" s="3">
-        <f>LEFT($F4, 1) &amp; LEFT($E4, 1)</f>
+        <f>$E4 &amp; " " &amp; LEFT($F4, 1) &amp; "."</f>
         <v/>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="G4" s="3">
-        <f>$F4 &amp; " -*- " &amp; $E4</f>
+        <f>$E4 &amp; " " &amp; $F4</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -586,12 +586,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Smithy</t>
         </is>
       </c>
       <c r="G2" s="3">
@@ -620,7 +620,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>John</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -581,12 +581,12 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>$E2 &amp; " " &amp; LEFT($F2, 1) &amp; "."</f>
+        <f>LEFT($E2, 1) &amp; "" &amp; LEFT($F2, 1)</f>
         <v/>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="G2" s="3">
-        <f>$E2 &amp; " " &amp; $F2</f>
+        <f>$E2 &amp; " - " &amp; $F2</f>
         <v/>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>$E3 &amp; " " &amp; LEFT($F3, 1) &amp; "."</f>
+        <f>LEFT($E3, 1) &amp; "" &amp; LEFT($F3, 1)</f>
         <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G3" s="3">
-        <f>$E3 &amp; " " &amp; $F3</f>
+        <f>$E3 &amp; " - " &amp; $F3</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D4" s="3">
-        <f>$E4 &amp; " " &amp; LEFT($F4, 1) &amp; "."</f>
+        <f>LEFT($E4, 1) &amp; "" &amp; LEFT($F4, 1)</f>
         <v/>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="G4" s="3">
-        <f>$E4 &amp; " " &amp; $F4</f>
+        <f>$E4 &amp; " - " &amp; $F4</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="G2" s="3">
-        <f>$E2 &amp; " - " &amp; $F2</f>
+        <f>$E2 &amp; " " &amp; $F2</f>
         <v/>
       </c>
     </row>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G3" s="3">
-        <f>$E3 &amp; " - " &amp; $F3</f>
+        <f>$E3 &amp; " " &amp; $F3</f>
         <v/>
       </c>
     </row>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="G4" s="3">
-        <f>$E4 &amp; " - " &amp; $F4</f>
+        <f>$E4 &amp; " " &amp; $F4</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>LEFT($E2, 1) &amp; "" &amp; LEFT($F2, 1)</f>
+        <f>LEFT($E2, 1) &amp; "" &amp; LEFT($F2, 1) &amp; ""</f>
         <v/>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="G2" s="3">
-        <f>$E2 &amp; " " &amp; $F2</f>
+        <f>$E2 &amp; " ... " &amp; $F2</f>
         <v/>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>LEFT($E3, 1) &amp; "" &amp; LEFT($F3, 1)</f>
+        <f>LEFT($E3, 1) &amp; "" &amp; LEFT($F3, 1) &amp; ""</f>
         <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G3" s="3">
-        <f>$E3 &amp; " " &amp; $F3</f>
+        <f>$E3 &amp; " ... " &amp; $F3</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D4" s="3">
-        <f>LEFT($E4, 1) &amp; "" &amp; LEFT($F4, 1)</f>
+        <f>LEFT($E4, 1) &amp; "" &amp; LEFT($F4, 1) &amp; ""</f>
         <v/>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -663,7 +663,41 @@
         </is>
       </c>
       <c r="G4" s="3">
-        <f>$E4 &amp; " " &amp; $F4</f>
+        <f>$E4 &amp; " ... " &amp; $F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>alice-cooper</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE($C5, "@", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>alice@cooper.com</t>
+        </is>
+      </c>
+      <c r="D5" s="3">
+        <f>LEFT($E5, 1) &amp; "" &amp; LEFT($F5, 1) &amp; ""</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Dangerfields</t>
+        </is>
+      </c>
+      <c r="G5" s="3">
+        <f>$E5 &amp; " ... " &amp; $F5</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -581,12 +581,12 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>LEFT($E2, 1) &amp; "" &amp; LEFT($F2, 1) &amp; ""</f>
+        <f>LEFT($E2, 1) &amp; LEFT($F2, 1)</f>
         <v/>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="G2" s="3">
-        <f>$E2 &amp; " ... " &amp; $F2</f>
+        <f>$F2 &amp; " " &amp; $E2</f>
         <v/>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>LEFT($E3, 1) &amp; "" &amp; LEFT($F3, 1) &amp; ""</f>
+        <f>LEFT($E3, 1) &amp; LEFT($F3, 1)</f>
         <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G3" s="3">
-        <f>$E3 &amp; " ... " &amp; $F3</f>
+        <f>$F3 &amp; " " &amp; $E3</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D4" s="3">
-        <f>LEFT($E4, 1) &amp; "" &amp; LEFT($F4, 1) &amp; ""</f>
+        <f>LEFT($E4, 1) &amp; LEFT($F4, 1)</f>
         <v/>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="G4" s="3">
-        <f>$E4 &amp; " ... " &amp; $F4</f>
+        <f>$F4 &amp; " " &amp; $E4</f>
         <v/>
       </c>
     </row>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D5" s="3">
-        <f>LEFT($E5, 1) &amp; "" &amp; LEFT($F5, 1) &amp; ""</f>
+        <f>LEFT($E5, 1) &amp; LEFT($F5, 1)</f>
         <v/>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,11 +693,11 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Dangerfields</t>
+          <t>Cooper</t>
         </is>
       </c>
       <c r="G5" s="3">
-        <f>$E5 &amp; " ... " &amp; $F5</f>
+        <f>$F5 &amp; " " &amp; $E5</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -165,22 +165,17 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Thec ustomers email address</t>
+        <t>First Name of the customer - used to make the full name</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>dsfdfds</t>
+        <t>Last Name of the customer - used to make the full name</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>First Name of the customer - used to make the full name</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Last Name of the customer - used to make the full name</t>
+        <t>dsfdfds</t>
       </text>
     </comment>
   </commentList>
@@ -511,15 +506,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,22 +529,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>EmailAddress</t>
+          <t>FirstName</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>LastName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Initials</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>FirstName</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LastName</t>
         </is>
       </c>
     </row>
@@ -561,27 +550,22 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>$F2 &amp; ", " &amp; $E2</f>
+        <f>$C2 &amp; " " &amp; $D2 </f>
         <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>jane.smith@email.com</t>
-        </is>
-      </c>
-      <c r="D2" s="3">
-        <f>LEFT($E2, 1) &amp; LEFT($F2, 1) &amp; "."</f>
-        <v/>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
           <t>Jane</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Smithy</t>
         </is>
+      </c>
+      <c r="E2" s="3">
+        <f>LEFT($C2, 1) &amp; LEFT($D2, 1) &amp; "."</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -591,27 +575,22 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>$F3 &amp; ", " &amp; $E3</f>
+        <f>$C3 &amp; " " &amp; $D3 </f>
         <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>john.doe@email.com</t>
-        </is>
-      </c>
-      <c r="D3" s="3">
-        <f>LEFT($E3, 1) &amp; LEFT($F3, 1) &amp; "."</f>
-        <v/>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
           <t>John</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Doe</t>
         </is>
+      </c>
+      <c r="E3" s="3">
+        <f>LEFT($C3, 1) &amp; LEFT($D3, 1) &amp; "."</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -621,27 +600,22 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>$F4 &amp; ", " &amp; $E4</f>
+        <f>$C4 &amp; " " &amp; $D4 </f>
         <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>emily.jones@email.com</t>
-        </is>
-      </c>
-      <c r="D4" s="3">
-        <f>LEFT($E4, 1) &amp; LEFT($F4, 1) &amp; "."</f>
-        <v/>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
           <t>Emily</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Jones</t>
         </is>
+      </c>
+      <c r="E4" s="3">
+        <f>LEFT($C4, 1) &amp; LEFT($D4, 1) &amp; "."</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -651,27 +625,22 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>$F5 &amp; ", " &amp; $E5</f>
+        <f>$C5 &amp; " " &amp; $D5 </f>
         <v/>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>alice@cooper.com</t>
-        </is>
-      </c>
-      <c r="D5" s="3">
-        <f>LEFT($E5, 1) &amp; LEFT($F5, 1) &amp; "."</f>
-        <v/>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Gutknecht</t>
-        </is>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Cooper</t>
+        </is>
+      </c>
+      <c r="E5" s="3">
+        <f>LEFT($C5, 1) &amp; LEFT($D5, 1) &amp; "."</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>LEFT($E2, 1) &amp; LEFT($F2, 1)</f>
+        <f>LEFT($E2, 1) &amp; LEFT($F2, 1) &amp; "-v3"</f>
         <v/>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>LEFT($E3, 1) &amp; LEFT($F3, 1)</f>
+        <f>LEFT($E3, 1) &amp; LEFT($F3, 1) &amp; "-v3"</f>
         <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" s="3">
-        <f>LEFT($E4, 1) &amp; LEFT($F4, 1)</f>
+        <f>LEFT($E4, 1) &amp; LEFT($F4, 1) &amp; "-v3"</f>
         <v/>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="D5" s="3">
-        <f>LEFT($E5, 1) &amp; LEFT($F5, 1)</f>
+        <f>LEFT($E5, 1) &amp; LEFT($F5, 1) &amp; "-v3"</f>
         <v/>
       </c>
       <c r="E5" s="2" t="inlineStr">

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>LEFT($E2, 1) &amp; LEFT($F2, 1) &amp; "-v3"</f>
+        <f>LEFT($E2, 1) &amp; LEFT($F2, 1)</f>
         <v/>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>LEFT($E3, 1) &amp; LEFT($F3, 1) &amp; "-v3"</f>
+        <f>LEFT($E3, 1) &amp; LEFT($F3, 1)</f>
         <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" s="3">
-        <f>LEFT($E4, 1) &amp; LEFT($F4, 1) &amp; "-v3"</f>
+        <f>LEFT($E4, 1) &amp; LEFT($F4, 1)</f>
         <v/>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="D5" s="3">
-        <f>LEFT($E5, 1) &amp; LEFT($F5, 1) &amp; "-v3"</f>
+        <f>LEFT($E5, 1) &amp; LEFT($F5, 1)</f>
         <v/>
       </c>
       <c r="E5" s="2" t="inlineStr">

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>$F2 &amp; ", " &amp; $E2</f>
+        <f>$F2 &amp; ", " &amp; $E2 &amp; " - v4"</f>
         <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>$F3 &amp; ", " &amp; $E3</f>
+        <f>$F3 &amp; ", " &amp; $E3 &amp; " - v4"</f>
         <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>$F4 &amp; ", " &amp; $E4</f>
+        <f>$F4 &amp; ", " &amp; $E4 &amp; " - v4"</f>
         <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>$F5 &amp; ", " &amp; $E5</f>
+        <f>$F5 &amp; ", " &amp; $E5 &amp; " - v4"</f>
         <v/>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Gutknecht</t>
+          <t>Gutknechts</t>
         </is>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>$F2 &amp; ", " &amp; $E2 &amp; " - v4"</f>
+        <f>$F2 &amp; ": " &amp; $E2 &amp; " - v5"</f>
         <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>$F3 &amp; ", " &amp; $E3 &amp; " - v4"</f>
+        <f>$F3 &amp; ": " &amp; $E3 &amp; " - v5"</f>
         <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>$F4 &amp; ", " &amp; $E4 &amp; " - v4"</f>
+        <f>$F4 &amp; ": " &amp; $E4 &amp; " - v5"</f>
         <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>$F5 &amp; ", " &amp; $E5 &amp; " - v4"</f>
+        <f>$F5 &amp; ": " &amp; $E5 &amp; " - v5"</f>
         <v/>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Gutknechts</t>
+          <t>Gutknecht</t>
         </is>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>$F2 &amp; ": " &amp; $E2 &amp; " - v5"</f>
+        <f>$F2 &amp; ", " &amp; $E2 &amp; " - v6"</f>
         <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>$F3 &amp; ": " &amp; $E3 &amp; " - v5"</f>
+        <f>$F3 &amp; ", " &amp; $E3 &amp; " - v6"</f>
         <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>$F4 &amp; ": " &amp; $E4 &amp; " - v5"</f>
+        <f>$F4 &amp; ", " &amp; $E4 &amp; " - v6"</f>
         <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>$F5 &amp; ": " &amp; $E5 &amp; " - v5"</f>
+        <f>$F5 &amp; ", " &amp; $E5 &amp; " - v6"</f>
         <v/>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Gutknecht</t>
+          <t>Mary</t>
         </is>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -160,57 +160,22 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Full name is computed from the first and last name of the customer</t>
+        <t>First Name of the customer</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>First Name of the customer - used to make the full name</t>
+        <t>Last Name of the customer</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Last Name of the customer - used to make the full name</t>
+        <t>Full name: first and last</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>dsfdfds</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>ERB Rulebook</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>The metadata key (e.g. 'tagline', 'motif_palette', 'substrates'). Unique within the table.</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Identifier for this metadata entry. Mirrors MetaKey so the row is addressable by Name like every other table.</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>How to interpret the value columns: 'string' (use StringValue), 'object' (parse JsonValue as JSON object), 'array' (parse JsonValue as JSON array).</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Plain string value. Populated when ValueType == 'string'; null otherwise.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>JSON-encoded value. Populated when ValueType == 'object' or 'array'; null when ValueType == 'string'.</t>
+        <t>Last letter of first and last name, dot-separated with trailing dot</t>
       </text>
     </comment>
   </commentList>
@@ -524,17 +489,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>FirstName</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LastName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>FirstName</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LastName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -549,22 +514,22 @@
           <t>jane-smith-email-com</t>
         </is>
       </c>
-      <c r="B2" s="3">
-        <f>$C2 &amp; " " &amp; $D2 </f>
-        <v/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
           <t>Smithy</t>
         </is>
       </c>
+      <c r="D2" s="3">
+        <f>$B2 &amp; " " &amp; $C2</f>
+        <v/>
+      </c>
       <c r="E2" s="3">
-        <f>LEFT($C2, 1) &amp; LEFT($D2, 1) &amp; "."</f>
+        <f>RIGHT($B2, 1) &amp; "." &amp; RIGHT($C2, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -574,22 +539,22 @@
           <t>john-doe-email-com</t>
         </is>
       </c>
-      <c r="B3" s="3">
-        <f>$C3 &amp; " " &amp; $D3 </f>
-        <v/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
           <t>Doe</t>
         </is>
       </c>
+      <c r="D3" s="3">
+        <f>$B3 &amp; " " &amp; $C3</f>
+        <v/>
+      </c>
       <c r="E3" s="3">
-        <f>LEFT($C3, 1) &amp; LEFT($D3, 1) &amp; "."</f>
+        <f>RIGHT($B3, 1) &amp; "." &amp; RIGHT($C3, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -599,22 +564,22 @@
           <t>emily-jones-email-com</t>
         </is>
       </c>
-      <c r="B4" s="3">
-        <f>$C4 &amp; " " &amp; $D4 </f>
-        <v/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
           <t>Jones</t>
         </is>
       </c>
+      <c r="D4" s="3">
+        <f>$B4 &amp; " " &amp; $C4</f>
+        <v/>
+      </c>
       <c r="E4" s="3">
-        <f>LEFT($C4, 1) &amp; LEFT($D4, 1) &amp; "."</f>
+        <f>RIGHT($B4, 1) &amp; "." &amp; RIGHT($C4, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -624,22 +589,22 @@
           <t>alice-cooper</t>
         </is>
       </c>
-      <c r="B5" s="3">
-        <f>$C5 &amp; " " &amp; $D5 </f>
-        <v/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Alice</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Cooper</t>
-        </is>
+          <t>Gutknechts</t>
+        </is>
+      </c>
+      <c r="D5" s="3">
+        <f>$B5 &amp; " " &amp; $C5</f>
+        <v/>
       </c>
       <c r="E5" s="3">
-        <f>LEFT($C5, 1) &amp; LEFT($D5, 1) &amp; "."</f>
+        <f>RIGHT($B5, 1) &amp; "." &amp; RIGHT($C5, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -655,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -692,185 +657,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>tagline</t>
-        </is>
-      </c>
-      <c r="B2" s="3">
-        <f>$A2</f>
-        <v/>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>One table. One calculated field. That's the whole demo.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>motif</t>
-        </is>
-      </c>
-      <c r="B3" s="3">
-        <f>$A3</f>
-        <v/>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>description_rich</t>
-        </is>
-      </c>
-      <c r="B4" s="3">
-        <f>$A4</f>
-        <v/>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>The smallest non-trivial Effortless rulebook. **One** entity (`Customers`), three rows, and a single calculated field — `FullName = FirstName &amp; " " &amp; LastName`. The argument is the simplicity itself: this much logic, lifted out of application code and into the rulebook, propagates to every substrate. Postgres view, Python class, Excel cell, OWL ontology — all four compute the same answer the same way, from the same rulebook JSON, with zero glue code.
-This is the rulebook to point a skeptic at when *every other demo feels like too much*.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>use_cases</t>
-        </is>
-      </c>
-      <c r="B5" s="3">
-        <f>$A5</f>
-        <v/>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>["**Edit `FirstName` on any row and watch `FullName` recompute in every substrate.** No application code reads this field — the rulebook IS the field.", "**Compare the Postgres view, the Python class, and the Excel cell** for the same row. They all compute `FullName` from the same formula declared once in the rulebook.", "**Try adding a calculated field of your own** — say `Initials = LEFT(FirstName, 1) &amp; LEFT(LastName, 1)`. Run `effortless build`. Every substrate now has it."]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>signature_rows</t>
-        </is>
-      </c>
-      <c r="B6" s="3">
-        <f>$A6</f>
-        <v/>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>[{"entity": "Customers", "ids": ["jane-smith-email-com", "john-doe-email-com", "emily-jones-email-com"]}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>journal_seed</t>
-        </is>
-      </c>
-      <c r="B7" s="3">
-        <f>$A7</f>
-        <v/>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Three customers. One calculated field. The whole point of ERB, on a napkin.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>substrates</t>
-        </is>
-      </c>
-      <c r="B8" s="3">
-        <f>$A8</f>
-        <v/>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>[{"key": "postgres", "important": true, "chip_label": "Postgres"}, {"key": "python", "important": true, "chip_label": "Python"}, {"key": "excel", "important": false, "chip_label": "Excel"}, {"key": "owl", "important": false, "chip_label": "OWL"}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>motif_palette</t>
-        </is>
-      </c>
-      <c r="B9" s="3">
-        <f>$A9</f>
-        <v/>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>{"primary": "#2b4a6a", "accent": "#e6a544", "ink": "#0d1b2a"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -521,15 +521,15 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Smithy</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D2" s="3">
-        <f>$B2 &amp; " " &amp; $C2</f>
+        <f>$C2 &amp; ", " &amp; $B2</f>
         <v/>
       </c>
       <c r="E2" s="3">
-        <f>RIGHT($B2, 1) &amp; "." &amp; RIGHT($C2, 1) &amp; "."</f>
+        <f>LEFT($B2, 1) &amp; ". " &amp; LEFT($C2, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -550,11 +550,11 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>$B3 &amp; " " &amp; $C3</f>
+        <f>$C3 &amp; ", " &amp; $B3</f>
         <v/>
       </c>
       <c r="E3" s="3">
-        <f>RIGHT($B3, 1) &amp; "." &amp; RIGHT($C3, 1) &amp; "."</f>
+        <f>LEFT($B3, 1) &amp; ". " &amp; LEFT($C3, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="D4" s="3">
-        <f>$B4 &amp; " " &amp; $C4</f>
+        <f>$C4 &amp; ", " &amp; $B4</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>RIGHT($B4, 1) &amp; "." &amp; RIGHT($C4, 1) &amp; "."</f>
+        <f>LEFT($B4, 1) &amp; ". " &amp; LEFT($C4, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -596,15 +596,15 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Gutknechts</t>
+          <t>Gutknecht</t>
         </is>
       </c>
       <c r="D5" s="3">
-        <f>$B5 &amp; " " &amp; $C5</f>
+        <f>$C5 &amp; ", " &amp; $B5</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>RIGHT($B5, 1) &amp; "." &amp; RIGHT($C5, 1) &amp; "."</f>
+        <f>LEFT($B5, 1) &amp; ". " &amp; LEFT($C5, 1) &amp; "."</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Smithy</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D2" s="3">
@@ -529,7 +529,7 @@
         <v/>
       </c>
       <c r="E2" s="3">
-        <f>RIGHT($B2, 1) &amp; "." &amp; RIGHT($C2, 1) &amp; "."</f>
+        <f>LEFT($B2, 1) &amp; "." &amp; LEFT($C2, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -554,7 +554,7 @@
         <v/>
       </c>
       <c r="E3" s="3">
-        <f>RIGHT($B3, 1) &amp; "." &amp; RIGHT($C3, 1) &amp; "."</f>
+        <f>LEFT($B3, 1) &amp; "." &amp; LEFT($C3, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -579,7 +579,7 @@
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>RIGHT($B4, 1) &amp; "." &amp; RIGHT($C4, 1) &amp; "."</f>
+        <f>LEFT($B4, 1) &amp; "." &amp; LEFT($C4, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Gutknechts</t>
+          <t>Gutknecht</t>
         </is>
       </c>
       <c r="D5" s="3">
@@ -604,7 +604,7 @@
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>RIGHT($B5, 1) &amp; "." &amp; RIGHT($C5, 1) &amp; "."</f>
+        <f>LEFT($B5, 1) &amp; "." &amp; LEFT($C5, 1) &amp; "."</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -529,7 +529,7 @@
         <v/>
       </c>
       <c r="E2" s="3">
-        <f>LEFT($B2, 1) &amp; "." &amp; LEFT($C2, 1) &amp; "."</f>
+        <f>LEFT($B2, 1) &amp; ". " &amp; LEFT($C2, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -554,7 +554,7 @@
         <v/>
       </c>
       <c r="E3" s="3">
-        <f>LEFT($B3, 1) &amp; "." &amp; LEFT($C3, 1) &amp; "."</f>
+        <f>LEFT($B3, 1) &amp; ". " &amp; LEFT($C3, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -579,7 +579,7 @@
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>LEFT($B4, 1) &amp; "." &amp; LEFT($C4, 1) &amp; "."</f>
+        <f>LEFT($B4, 1) &amp; ". " &amp; LEFT($C4, 1) &amp; "."</f>
         <v/>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>LEFT($B5, 1) &amp; "." &amp; LEFT($C5, 1) &amp; "."</f>
+        <f>LEFT($B5, 1) &amp; ". " &amp; LEFT($C5, 1) &amp; "."</f>
         <v/>
       </c>
     </row>

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="D2" s="3">
-        <f>$B2 &amp; " " &amp; $C2</f>
+        <f>$C2 &amp; ", " &amp; $B2</f>
         <v/>
       </c>
       <c r="E2" s="3">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>$B3 &amp; " " &amp; $C3</f>
+        <f>$C3 &amp; ", " &amp; $B3</f>
         <v/>
       </c>
       <c r="E3" s="3">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D4" s="3">
-        <f>$B4 &amp; " " &amp; $C4</f>
+        <f>$C4 &amp; ", " &amp; $B4</f>
         <v/>
       </c>
       <c r="E4" s="3">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D5" s="3">
-        <f>$B5 &amp; " " &amp; $C5</f>
+        <f>$C5 &amp; ", " &amp; $B5</f>
         <v/>
       </c>
       <c r="E5" s="3">

--- a/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
+++ b/rulebook-examples/customer-fullname/xlsx/rulebook.xlsx
@@ -1,53 +1,211 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eejai42/effortlessapi-app-root/users/user_ee42ai73-18a9-47d5-8f99-954b00f6c041/my-projects/effortless-rulebooks/rulebook-examples/customer-fullname/xlsx/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49462916-CC4E-5449-A3ED-B3B8765EEA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__meta__" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Customers" sheetId="1" r:id="rId1"/>
+    <sheet name="__meta__" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>First Name of the customer</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Last Name of the customer</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Full name: first and last</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Last letter of first and last name, dot-separated with trailing dot</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>CustomerId</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Initials</t>
+  </si>
+  <si>
+    <t>jane-smith-email-com</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>john-doe-email-com</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>emily-jones-email-com</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>Jones</t>
+  </si>
+  <si>
+    <t>alice-cooper</t>
+  </si>
+  <si>
+    <t>Gutknecht</t>
+  </si>
+  <si>
+    <t>MetaKey</t>
+  </si>
+  <si>
+    <t>ValueType</t>
+  </si>
+  <si>
+    <t>StringValue</t>
+  </si>
+  <si>
+    <t>JsonValue</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-        <bgColor rgb="00DDEBF7"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,126 +218,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>ERB Rulebook</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>First Name of the customer</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Last Name of the customer</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Full name: first and last</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Last letter of first and last name, dot-separated with trailing dot</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -466,195 +544,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CustomerId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>FirstName</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LastName</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Initials</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>jane-smith-email-com</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Jane</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="D2" s="3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="str">
         <f>$C2 &amp; ", " &amp; $B2</f>
-        <v/>
-      </c>
-      <c r="E2" s="3">
-        <f>LEFT($B2, 1) &amp; ". " &amp; LEFT($C2, 1) &amp; "."</f>
-        <v/>
+        <v>Smith, Jane</v>
+      </c>
+      <c r="E2" s="3" t="str">
+        <f>LEFT($B2, 1) &amp;LEFT($C2, 1) &amp; "-v2"</f>
+        <v>JS-v2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>john-doe-email-com</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Doe</t>
-        </is>
-      </c>
-      <c r="D3" s="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="str">
         <f>$C3 &amp; ", " &amp; $B3</f>
-        <v/>
-      </c>
-      <c r="E3" s="3">
-        <f>LEFT($B3, 1) &amp; ". " &amp; LEFT($C3, 1) &amp; "."</f>
-        <v/>
+        <v>Doe, John</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <f t="shared" ref="E3:E5" si="0">LEFT($B3, 1) &amp;LEFT($C3, 1) &amp; "-v2"</f>
+        <v>JD-v2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>emily-jones-email-com</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Emily</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="D4" s="3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="str">
         <f>$C4 &amp; ", " &amp; $B4</f>
-        <v/>
-      </c>
-      <c r="E4" s="3">
-        <f>LEFT($B4, 1) &amp; ". " &amp; LEFT($C4, 1) &amp; "."</f>
-        <v/>
+        <v>Jones, Emily</v>
+      </c>
+      <c r="E4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>EJ-v2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>alice-cooper</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Alice</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Gutknecht</t>
-        </is>
-      </c>
-      <c r="D5" s="3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="str">
         <f>$C5 &amp; ", " &amp; $B5</f>
-        <v/>
-      </c>
-      <c r="E5" s="3">
-        <f>LEFT($B5, 1) &amp; ". " &amp; LEFT($C5, 1) &amp; "."</f>
-        <v/>
+        <v>Gutknecht, Mary</v>
+      </c>
+      <c r="E5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>MG-v2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MetaKey</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ValueType</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>StringValue</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>JsonValue</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
